--- a/data/trans_orig/IQ27-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IQ27-Edad-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Peso medio, en kilogramos, referido por progenitor/a</t>
+          <t>Peso medio, en kilogramos, declarado por progenitor/a (tasa de respuesta: 96,01%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>10,39; 11,64</t>
+          <t>10,38; 11,68</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>9,64; 10,64</t>
+          <t>9,71; 10,68</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9,68; 10,56</t>
+          <t>9,69; 10,6</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>13,31; 17,43</t>
+          <t>13,29; 16,94</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>10,55; 11,72</t>
+          <t>10,54; 11,65</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,99; 10,91</t>
+          <t>10,02; 10,97</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,24; 11,29</t>
+          <t>10,26; 11,33</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>11,83; 14,36</t>
+          <t>11,71; 14,4</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>10,6; 11,46</t>
+          <t>10,63; 11,45</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>10,02; 10,68</t>
+          <t>10,0; 10,68</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>10,09; 10,77</t>
+          <t>10,12; 10,78</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>12,82; 15,2</t>
+          <t>12,75; 15,1</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>21,09; 22,42</t>
+          <t>21,13; 22,55</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>20,86; 22,23</t>
+          <t>20,84; 22,18</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>20,76; 22,15</t>
+          <t>20,74; 22,12</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>21,75; 24,25</t>
+          <t>21,8; 24,23</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>21,86; 23,1</t>
+          <t>21,83; 23,09</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>21,4; 22,73</t>
+          <t>21,42; 22,72</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>20,97; 22,16</t>
+          <t>20,97; 22,14</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>24,41; 27,71</t>
+          <t>24,64; 27,92</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>21,66; 22,62</t>
+          <t>21,66; 22,58</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>21,31; 22,24</t>
+          <t>21,34; 22,24</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>21,01; 21,88</t>
+          <t>21,01; 21,92</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>23,59; 25,74</t>
+          <t>23,43; 25,75</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>36,68; 39,38</t>
+          <t>36,58; 39,32</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>35,91; 38,41</t>
+          <t>35,77; 38,32</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>34,65; 36,76</t>
+          <t>34,66; 36,77</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>33,46; 37,26</t>
+          <t>33,3; 37,15</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>36,76; 39,32</t>
+          <t>36,69; 39,14</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>35,26; 37,4</t>
+          <t>35,3; 37,43</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>35,79; 37,97</t>
+          <t>35,84; 37,98</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>35,28; 38,97</t>
+          <t>35,15; 38,98</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>37,04; 38,83</t>
+          <t>37,03; 38,9</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>35,79; 37,48</t>
+          <t>35,81; 37,45</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>35,5; 37,03</t>
+          <t>35,54; 36,98</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>34,93; 37,54</t>
+          <t>34,92; 37,53</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>50,81; 52,72</t>
+          <t>50,84; 52,82</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>49,96; 52,9</t>
+          <t>50,03; 52,94</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>49,69; 52,26</t>
+          <t>49,58; 52,19</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>43,55; 50,58</t>
+          <t>43,31; 50,32</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>57,33; 60,16</t>
+          <t>57,41; 60,05</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>54,19; 57,61</t>
+          <t>54,19; 57,62</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>52,32; 55,79</t>
+          <t>52,52; 55,71</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>48,42; 53,42</t>
+          <t>48,34; 53,35</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>54,49; 56,18</t>
+          <t>54,45; 56,18</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>52,52; 54,85</t>
+          <t>52,53; 54,73</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>51,42; 53,53</t>
+          <t>51,38; 53,5</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>46,73; 51,09</t>
+          <t>46,75; 50,72</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>30,58; 32,7</t>
+          <t>30,74; 32,8</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>28,73; 30,91</t>
+          <t>28,72; 30,82</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>29,08; 31,15</t>
+          <t>29,07; 31,1</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>33,43; 38,48</t>
+          <t>33,25; 39,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>32,79; 35,17</t>
+          <t>32,83; 35,19</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>29,52; 31,89</t>
+          <t>29,67; 32,01</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>29,86; 31,96</t>
+          <t>29,94; 32,09</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>36,18; 39,47</t>
+          <t>36,38; 39,59</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>32,09; 33,71</t>
+          <t>32,11; 33,67</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>29,51; 31,15</t>
+          <t>29,54; 31,01</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>29,8; 31,25</t>
+          <t>29,82; 31,29</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>35,29; 38,41</t>
+          <t>35,32; 38,26</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ27-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IQ27-Edad-trans_orig.xlsx
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>10,38; 11,68</t>
+          <t>10,38; 11,69</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>9,71; 10,68</t>
+          <t>9,69; 10,7</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9,69; 10,6</t>
+          <t>9,68; 10,59</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>13,29; 16,94</t>
+          <t>13,32; 17,31</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>10,54; 11,65</t>
+          <t>10,56; 11,75</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>10,02; 10,97</t>
+          <t>10,02; 10,99</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,26; 11,33</t>
+          <t>10,25; 11,25</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>11,71; 14,4</t>
+          <t>11,85; 14,38</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>10,63; 11,45</t>
+          <t>10,62; 11,51</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>10,0; 10,68</t>
+          <t>9,98; 10,69</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>10,12; 10,78</t>
+          <t>10,09; 10,78</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>12,75; 15,1</t>
+          <t>12,88; 15,01</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>21,13; 22,55</t>
+          <t>21,1; 22,44</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>20,84; 22,18</t>
+          <t>20,86; 22,18</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>20,74; 22,12</t>
+          <t>20,71; 22,08</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>21,8; 24,23</t>
+          <t>21,73; 24,27</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>21,83; 23,09</t>
+          <t>21,84; 23,06</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>21,42; 22,72</t>
+          <t>21,33; 22,67</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>20,97; 22,14</t>
+          <t>20,93; 22,14</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>24,64; 27,92</t>
+          <t>24,44; 27,87</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>21,66; 22,58</t>
+          <t>21,62; 22,58</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>21,34; 22,24</t>
+          <t>21,31; 22,24</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>21,01; 21,92</t>
+          <t>20,99; 21,9</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>23,43; 25,75</t>
+          <t>23,65; 25,8</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>36,58; 39,32</t>
+          <t>36,64; 39,41</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>35,77; 38,32</t>
+          <t>35,76; 38,14</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>34,66; 36,77</t>
+          <t>34,58; 36,65</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>33,3; 37,15</t>
+          <t>33,56; 37,3</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>36,69; 39,14</t>
+          <t>36,84; 39,24</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>35,3; 37,43</t>
+          <t>35,17; 37,34</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>35,84; 37,98</t>
+          <t>35,72; 37,96</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>35,15; 38,98</t>
+          <t>35,27; 39,19</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>37,03; 38,9</t>
+          <t>37,11; 38,93</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>35,81; 37,45</t>
+          <t>35,81; 37,55</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>35,54; 36,98</t>
+          <t>35,58; 37,04</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>34,92; 37,53</t>
+          <t>34,93; 37,72</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>50,84; 52,82</t>
+          <t>50,67; 52,63</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>50,03; 52,94</t>
+          <t>50,11; 53,15</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>49,58; 52,19</t>
+          <t>49,64; 52,18</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>43,31; 50,32</t>
+          <t>43,4; 50,19</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>57,41; 60,05</t>
+          <t>57,37; 60,15</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>54,19; 57,62</t>
+          <t>54,16; 57,56</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>52,52; 55,71</t>
+          <t>52,51; 55,8</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>48,34; 53,35</t>
+          <t>48,41; 53,58</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>54,45; 56,18</t>
+          <t>54,53; 56,19</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>52,53; 54,73</t>
+          <t>52,55; 54,88</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>51,38; 53,5</t>
+          <t>51,32; 53,46</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>46,75; 50,72</t>
+          <t>46,43; 50,62</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>30,74; 32,8</t>
+          <t>30,67; 32,74</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>28,72; 30,82</t>
+          <t>28,74; 30,97</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>29,07; 31,1</t>
+          <t>29,11; 31,11</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>33,25; 39,0</t>
+          <t>33,3; 38,77</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>32,83; 35,19</t>
+          <t>32,76; 35,15</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>29,67; 32,01</t>
+          <t>29,68; 32,02</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>29,94; 32,09</t>
+          <t>29,84; 31,96</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>36,38; 39,59</t>
+          <t>36,28; 39,49</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>32,11; 33,67</t>
+          <t>32,02; 33,58</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>29,54; 31,01</t>
+          <t>29,51; 31,06</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>29,82; 31,29</t>
+          <t>29,76; 31,2</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>35,32; 38,26</t>
+          <t>35,36; 38,05</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ27-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IQ27-Edad-trans_orig.xlsx
@@ -532,7 +532,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -540,7 +540,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -648,42 +648,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>11,1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>10,49</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>10,75</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>12,7</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>10,97</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>10,17</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>10,13</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>14,87</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>11,1</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>10,49</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>10,75</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>12,82</t>
+          <t>15,19</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>13,81</t>
+          <t>13,96</t>
         </is>
       </c>
     </row>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>10,38; 11,69</t>
+          <t>10,55; 11,72</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>9,69; 10,7</t>
+          <t>9,99; 10,91</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9,68; 10,59</t>
+          <t>10,24; 11,29</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>13,32; 17,31</t>
+          <t>11,81; 14,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>10,56; 11,75</t>
+          <t>10,39; 11,64</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>10,02; 10,99</t>
+          <t>9,64; 10,64</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,25; 11,25</t>
+          <t>9,68; 10,56</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>11,85; 14,38</t>
+          <t>13,58; 17,6</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>10,62; 11,51</t>
+          <t>10,6; 11,46</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9,98; 10,69</t>
+          <t>10,02; 10,68</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>10,09; 10,78</t>
+          <t>10,09; 10,77</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>12,88; 15,01</t>
+          <t>12,94; 15,35</t>
         </is>
       </c>
     </row>
@@ -788,42 +788,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>22,44</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>22,02</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>21,54</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>26,15</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>21,71</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>21,51</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>21,36</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>22,91</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>22,44</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>22,02</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>21,54</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>26,03</t>
+          <t>23,26</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>24,59</t>
+          <t>24,78</t>
         </is>
       </c>
     </row>
@@ -856,47 +856,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>21,1; 22,44</t>
+          <t>21,86; 23,1</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>20,86; 22,18</t>
+          <t>21,4; 22,73</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>20,71; 22,08</t>
+          <t>20,97; 22,16</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>21,73; 24,27</t>
+          <t>24,52; 27,86</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>21,84; 23,06</t>
+          <t>21,09; 22,42</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>21,33; 22,67</t>
+          <t>20,86; 22,23</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>20,93; 22,14</t>
+          <t>20,76; 22,15</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>24,44; 27,87</t>
+          <t>22,13; 24,66</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>21,62; 22,58</t>
+          <t>21,66; 22,62</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -906,12 +906,12 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>20,99; 21,9</t>
+          <t>21,01; 21,88</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>23,65; 25,8</t>
+          <t>23,77; 26,01</t>
         </is>
       </c>
     </row>
@@ -928,42 +928,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>37,96</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>36,31</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>36,84</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>37,33</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>37,87</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>36,94</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>35,64</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>35,18</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>37,96</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>36,31</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>36,84</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>37,08</t>
+          <t>34,95</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>36,21</t>
+          <t>36,2</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>36,64; 39,41</t>
+          <t>36,76; 39,32</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>35,76; 38,14</t>
+          <t>35,26; 37,4</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>34,58; 36,65</t>
+          <t>35,79; 37,97</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>33,56; 37,3</t>
+          <t>35,42; 39,26</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>36,84; 39,24</t>
+          <t>36,68; 39,38</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>35,17; 37,34</t>
+          <t>35,91; 38,41</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>35,72; 37,96</t>
+          <t>34,65; 36,76</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>35,27; 39,19</t>
+          <t>33,25; 36,95</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>37,11; 38,93</t>
+          <t>37,04; 38,83</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>35,81; 37,55</t>
+          <t>35,79; 37,48</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>35,58; 37,04</t>
+          <t>35,5; 37,03</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>34,93; 37,72</t>
+          <t>34,88; 37,52</t>
         </is>
       </c>
     </row>
@@ -1068,42 +1068,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>58,71</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>55,81</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>54,05</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>51,0</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>51,73</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>51,5</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>50,84</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>46,36</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>58,71</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>55,81</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>54,05</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>50,78</t>
+          <t>45,95</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>48,7</t>
+          <t>48,66</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>50,67; 52,63</t>
+          <t>57,33; 60,16</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>50,11; 53,15</t>
+          <t>54,19; 57,61</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>49,64; 52,18</t>
+          <t>52,32; 55,79</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>43,4; 50,19</t>
+          <t>48,68; 53,73</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>57,37; 60,15</t>
+          <t>50,81; 52,72</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>54,16; 57,56</t>
+          <t>49,96; 52,9</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>52,51; 55,8</t>
+          <t>49,69; 52,26</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>48,41; 53,58</t>
+          <t>44,26; 47,73</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>54,53; 56,19</t>
+          <t>54,49; 56,18</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>52,55; 54,88</t>
+          <t>52,52; 54,85</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>51,32; 53,46</t>
+          <t>51,42; 53,53</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>46,43; 50,62</t>
+          <t>47,13; 50,29</t>
         </is>
       </c>
     </row>
@@ -1208,42 +1208,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>33,98</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>30,75</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>30,89</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>38,48</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>31,68</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>29,79</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>30,09</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>34,89</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>33,98</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>30,75</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>30,89</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>37,73</t>
+          <t>34,84</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>36,41</t>
+          <t>36,76</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>30,67; 32,74</t>
+          <t>32,79; 35,17</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>28,74; 30,97</t>
+          <t>29,52; 31,89</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>29,11; 31,11</t>
+          <t>29,86; 31,96</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>33,3; 38,77</t>
+          <t>36,9; 40,17</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>32,76; 35,15</t>
+          <t>30,58; 32,7</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>29,68; 32,02</t>
+          <t>28,73; 30,91</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>29,84; 31,96</t>
+          <t>29,08; 31,15</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>36,28; 39,49</t>
+          <t>33,58; 36,03</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>32,02; 33,58</t>
+          <t>32,09; 33,71</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>29,51; 31,06</t>
+          <t>29,51; 31,15</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>29,76; 31,2</t>
+          <t>29,8; 31,25</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>35,36; 38,05</t>
+          <t>35,74; 37,88</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ27-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IQ27-Edad-trans_orig.xlsx
@@ -16,7 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +127,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +140,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +509,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N14"/>
+  <dimension ref="A1:N19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -526,7 +531,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Peso medio, en kilogramos, declarado por progenitor/a (tasa de respuesta: 96,01%)</t>
+          <t>Peso medio, en kilogramos, declarado por madres/padres (tasa de respuesta: 96,01%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -646,419 +651,271 @@
           <t>Media</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>11,1</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>10,49</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>10,75</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>12,7</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>10,97</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>10,17</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>10,13</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>15,19</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>11,04</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>10,33</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>10,43</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>13,96</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>11.09879608133846</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>10.48790371941043</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>10.75475049433135</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>12.69976027455016</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>10.9734231017886</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>10.16989448282903</v>
+      </c>
+      <c r="I4" s="5" t="n">
+        <v>10.13094467426201</v>
+      </c>
+      <c r="J4" s="5" t="n">
+        <v>15.18627762098421</v>
+      </c>
+      <c r="K4" s="5" t="n">
+        <v>11.04050566157643</v>
+      </c>
+      <c r="L4" s="5" t="n">
+        <v>10.32775103583069</v>
+      </c>
+      <c r="M4" s="5" t="n">
+        <v>10.43045146339206</v>
+      </c>
+      <c r="N4" s="5" t="n">
+        <v>13.96486501655046</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>10,55; 11,72</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>9,99; 10,91</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>10,24; 11,29</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>11,81; 14,0</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>10,39; 11,64</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>9,64; 10,64</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>9,68; 10,56</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>13,58; 17,6</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>10,6; 11,46</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>10,02; 10,68</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>10,09; 10,77</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>12,94; 15,35</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>10.55305288406217</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>9.990517342477633</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>10.2390811626491</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>11.80608583218503</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>10.39238342500964</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>9.643653862669183</v>
+      </c>
+      <c r="I5" s="5" t="n">
+        <v>9.679104945620015</v>
+      </c>
+      <c r="J5" s="5" t="n">
+        <v>13.57727014492237</v>
+      </c>
+      <c r="K5" s="5" t="n">
+        <v>10.59628421926303</v>
+      </c>
+      <c r="L5" s="5" t="n">
+        <v>10.02093890153312</v>
+      </c>
+      <c r="M5" s="5" t="n">
+        <v>10.08774100122119</v>
+      </c>
+      <c r="N5" s="5" t="n">
+        <v>12.94477259977861</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>11.72074979869779</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>10.9134219870263</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>11.29378951996602</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>13.99698574610913</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>11.63911956444077</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>10.63824641367926</v>
+      </c>
+      <c r="I6" s="5" t="n">
+        <v>10.55614772155663</v>
+      </c>
+      <c r="J6" s="5" t="n">
+        <v>17.59606898933066</v>
+      </c>
+      <c r="K6" s="5" t="n">
+        <v>11.46035401425975</v>
+      </c>
+      <c r="L6" s="5" t="n">
+        <v>10.67543299876921</v>
+      </c>
+      <c r="M6" s="5" t="n">
+        <v>10.7696770630879</v>
+      </c>
+      <c r="N6" s="5" t="n">
+        <v>15.35097761075093</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>3-7</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>22,44</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>22,02</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>21,54</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>26,15</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>21,71</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>21,51</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>21,36</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>23,26</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>22,07</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>21,78</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>21,46</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>24,78</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>21,86; 23,1</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>21,4; 22,73</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>20,97; 22,16</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>24,52; 27,86</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>21,09; 22,42</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>20,86; 22,23</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>20,76; 22,15</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>22,13; 24,66</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>21,66; 22,62</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>21,31; 22,24</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>21,01; 21,88</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>23,77; 26,01</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>22.44159258151106</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>22.02254266753612</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>21.54168840695448</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>26.1465934614807</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>21.70941344247634</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>21.50888491205676</v>
+      </c>
+      <c r="I7" s="5" t="n">
+        <v>21.36359355999906</v>
+      </c>
+      <c r="J7" s="5" t="n">
+        <v>23.26172831177414</v>
+      </c>
+      <c r="K7" s="5" t="n">
+        <v>22.07407757418071</v>
+      </c>
+      <c r="L7" s="5" t="n">
+        <v>21.78066391756106</v>
+      </c>
+      <c r="M7" s="5" t="n">
+        <v>21.4612743072618</v>
+      </c>
+      <c r="N7" s="5" t="n">
+        <v>24.78023027051482</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>8-11</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>37,96</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>36,31</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>36,84</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>37,33</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>37,87</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>36,94</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>35,64</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>34,95</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>37,92</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>36,62</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>36,24</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>36,2</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>21.85536856040422</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>21.40130999896742</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>20.96906258270506</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>24.52014819778943</v>
+      </c>
+      <c r="G8" s="5" t="n">
+        <v>21.09376520018645</v>
+      </c>
+      <c r="H8" s="5" t="n">
+        <v>20.86144316235763</v>
+      </c>
+      <c r="I8" s="5" t="n">
+        <v>20.75850553307102</v>
+      </c>
+      <c r="J8" s="5" t="n">
+        <v>22.12662676944212</v>
+      </c>
+      <c r="K8" s="5" t="n">
+        <v>21.65910044000372</v>
+      </c>
+      <c r="L8" s="5" t="n">
+        <v>21.31486248903906</v>
+      </c>
+      <c r="M8" s="5" t="n">
+        <v>21.00958405253503</v>
+      </c>
+      <c r="N8" s="5" t="n">
+        <v>23.77338971861076</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>36,76; 39,32</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>35,26; 37,4</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>35,79; 37,97</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>35,42; 39,26</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>36,68; 39,38</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>35,91; 38,41</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>34,65; 36,76</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>33,25; 36,95</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>37,04; 38,83</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>35,79; 37,48</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>35,5; 37,03</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>34,88; 37,52</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>23.10270520897658</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>22.73286584681531</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>22.16291068855827</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>27.86406159874031</v>
+      </c>
+      <c r="G9" s="5" t="n">
+        <v>22.42039576300378</v>
+      </c>
+      <c r="H9" s="5" t="n">
+        <v>22.22607907162669</v>
+      </c>
+      <c r="I9" s="5" t="n">
+        <v>22.14643682135838</v>
+      </c>
+      <c r="J9" s="5" t="n">
+        <v>24.658514549901</v>
+      </c>
+      <c r="K9" s="5" t="n">
+        <v>22.61966575235457</v>
+      </c>
+      <c r="L9" s="5" t="n">
+        <v>22.23620660626751</v>
+      </c>
+      <c r="M9" s="5" t="n">
+        <v>21.88432566780945</v>
+      </c>
+      <c r="N9" s="5" t="n">
+        <v>26.01459023971576</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>12-15</t>
+          <t>8-11</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -1066,277 +923,405 @@
           <t>Media</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>58,71</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>55,81</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>54,05</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>51,0</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>51,73</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>51,5</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>50,84</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>45,95</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>55,32</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>53,67</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>52,43</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>48,66</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>37.95813699649774</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>36.30906819384416</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>36.83697992400511</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>37.32950441714728</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>37.87040998147324</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>36.94155841442387</v>
+      </c>
+      <c r="I10" s="5" t="n">
+        <v>35.64279577316686</v>
+      </c>
+      <c r="J10" s="5" t="n">
+        <v>34.94881231581334</v>
+      </c>
+      <c r="K10" s="5" t="n">
+        <v>37.91615647542828</v>
+      </c>
+      <c r="L10" s="5" t="n">
+        <v>36.62384893630764</v>
+      </c>
+      <c r="M10" s="5" t="n">
+        <v>36.23566698455831</v>
+      </c>
+      <c r="N10" s="5" t="n">
+        <v>36.20369601429133</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>57,33; 60,16</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>54,19; 57,61</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>52,32; 55,79</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>48,68; 53,73</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>50,81; 52,72</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>49,96; 52,9</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>49,69; 52,26</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>44,26; 47,73</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>54,49; 56,18</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>52,52; 54,85</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>51,42; 53,53</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>47,13; 50,29</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>36.75867740646916</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>35.25668284119359</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>35.79428055953279</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>35.41954265450471</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>36.68088726688811</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>35.90683187994275</v>
+      </c>
+      <c r="I11" s="5" t="n">
+        <v>34.65400967814388</v>
+      </c>
+      <c r="J11" s="5" t="n">
+        <v>33.25498146134834</v>
+      </c>
+      <c r="K11" s="5" t="n">
+        <v>37.03634411173958</v>
+      </c>
+      <c r="L11" s="5" t="n">
+        <v>35.78519542110593</v>
+      </c>
+      <c r="M11" s="5" t="n">
+        <v>35.49919728878093</v>
+      </c>
+      <c r="N11" s="5" t="n">
+        <v>34.87869582752128</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>39.31750361430457</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>37.39963219923625</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>37.97391394319735</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>39.26434224787649</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>39.37626541740411</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>38.4066984375797</v>
+      </c>
+      <c r="I12" s="5" t="n">
+        <v>36.7572024653657</v>
+      </c>
+      <c r="J12" s="5" t="n">
+        <v>36.94980063603501</v>
+      </c>
+      <c r="K12" s="5" t="n">
+        <v>38.8327453852615</v>
+      </c>
+      <c r="L12" s="5" t="n">
+        <v>37.47954860079602</v>
+      </c>
+      <c r="M12" s="5" t="n">
+        <v>37.02817117326541</v>
+      </c>
+      <c r="N12" s="5" t="n">
+        <v>37.51906209626303</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>58.71279403246126</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>55.80875789980364</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>54.0500269258992</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>50.99763849653354</v>
+      </c>
+      <c r="G13" s="5" t="n">
+        <v>51.72612477722284</v>
+      </c>
+      <c r="H13" s="5" t="n">
+        <v>51.50378057420454</v>
+      </c>
+      <c r="I13" s="5" t="n">
+        <v>50.839917171743</v>
+      </c>
+      <c r="J13" s="5" t="n">
+        <v>45.95445839755779</v>
+      </c>
+      <c r="K13" s="5" t="n">
+        <v>55.32088642884028</v>
+      </c>
+      <c r="L13" s="5" t="n">
+        <v>53.67488146847381</v>
+      </c>
+      <c r="M13" s="5" t="n">
+        <v>52.42541266555066</v>
+      </c>
+      <c r="N13" s="5" t="n">
+        <v>48.66442703882298</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>57.3339281507215</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>54.188512676992</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>52.31543907537523</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>48.68261080888244</v>
+      </c>
+      <c r="G14" s="5" t="n">
+        <v>50.81021108036199</v>
+      </c>
+      <c r="H14" s="5" t="n">
+        <v>49.96360012649618</v>
+      </c>
+      <c r="I14" s="5" t="n">
+        <v>49.68919301847642</v>
+      </c>
+      <c r="J14" s="5" t="n">
+        <v>44.26230055397406</v>
+      </c>
+      <c r="K14" s="5" t="n">
+        <v>54.49049706203647</v>
+      </c>
+      <c r="L14" s="5" t="n">
+        <v>52.52155052012594</v>
+      </c>
+      <c r="M14" s="5" t="n">
+        <v>51.4180627796489</v>
+      </c>
+      <c r="N14" s="5" t="n">
+        <v>47.13337515556281</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>60.16469632066594</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>57.6131627741572</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>55.78876729659281</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>53.72615935451879</v>
+      </c>
+      <c r="G15" s="5" t="n">
+        <v>52.72304718482277</v>
+      </c>
+      <c r="H15" s="5" t="n">
+        <v>52.90289538737547</v>
+      </c>
+      <c r="I15" s="5" t="n">
+        <v>52.25503133983715</v>
+      </c>
+      <c r="J15" s="5" t="n">
+        <v>47.73157142229415</v>
+      </c>
+      <c r="K15" s="5" t="n">
+        <v>56.18299742027746</v>
+      </c>
+      <c r="L15" s="5" t="n">
+        <v>54.84530430072886</v>
+      </c>
+      <c r="M15" s="5" t="n">
+        <v>53.53210065360035</v>
+      </c>
+      <c r="N15" s="5" t="n">
+        <v>50.28810573308537</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>33,98</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>30,75</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>30,89</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>38,48</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>31,68</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>29,79</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>30,09</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>34,84</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>32,86</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>30,28</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>30,5</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>36,76</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>32,79; 35,17</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>29,52; 31,89</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>29,86; 31,96</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>36,9; 40,17</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>30,58; 32,7</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>28,73; 30,91</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>29,08; 31,15</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>33,58; 36,03</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>32,09; 33,71</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>29,51; 31,15</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>29,8; 31,25</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>35,74; 37,88</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="C16" s="5" t="n">
+        <v>33.97858178118736</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>30.74900930956836</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>30.89386384577849</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>38.4777046442728</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>31.67946562434066</v>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>29.79499231024989</v>
+      </c>
+      <c r="I16" s="5" t="n">
+        <v>30.09099794967194</v>
+      </c>
+      <c r="J16" s="5" t="n">
+        <v>34.83741900075168</v>
+      </c>
+      <c r="K16" s="5" t="n">
+        <v>32.85958149250187</v>
+      </c>
+      <c r="L16" s="5" t="n">
+        <v>30.2823536765403</v>
+      </c>
+      <c r="M16" s="5" t="n">
+        <v>30.50029104602862</v>
+      </c>
+      <c r="N16" s="5" t="n">
+        <v>36.76007697944866</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>32.78986677199755</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>29.52387587486694</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>29.85555003947752</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>36.90430442148803</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>30.58184131401931</v>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>28.73098424343596</v>
+      </c>
+      <c r="I17" s="5" t="n">
+        <v>29.07987545762241</v>
+      </c>
+      <c r="J17" s="5" t="n">
+        <v>33.58115039222896</v>
+      </c>
+      <c r="K17" s="5" t="n">
+        <v>32.09322742954793</v>
+      </c>
+      <c r="L17" s="5" t="n">
+        <v>29.51014300913656</v>
+      </c>
+      <c r="M17" s="5" t="n">
+        <v>29.79823078815953</v>
+      </c>
+      <c r="N17" s="5" t="n">
+        <v>35.74211893175089</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>35.16910291854562</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>31.88584827116886</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>31.96246024512977</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>40.1687301002037</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>32.69639658263149</v>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>30.90687813639867</v>
+      </c>
+      <c r="I18" s="5" t="n">
+        <v>31.14784056787221</v>
+      </c>
+      <c r="J18" s="5" t="n">
+        <v>36.02678730498279</v>
+      </c>
+      <c r="K18" s="5" t="n">
+        <v>33.71374599789781</v>
+      </c>
+      <c r="L18" s="5" t="n">
+        <v>31.15277743867667</v>
+      </c>
+      <c r="M18" s="5" t="n">
+        <v>31.24508485558694</v>
+      </c>
+      <c r="N18" s="5" t="n">
+        <v>37.8790480707251</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1344,15 +1329,15 @@
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
     <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
